--- a/floristics_data/transects/transect_metadata.xlsx
+++ b/floristics_data/transects/transect_metadata.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gwenr\Documents\Git\junction_floristics\floristics_data\transects\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4ACFB767-AFE7-4DF4-B1F6-4478CC1B9D13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12C1B47A-F5E6-4FE5-850F-57939ADEF0A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" xr2:uid="{1A0338C2-7AD1-4123-B4FE-0284DE0026AC}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="47">
   <si>
     <t>column_name</t>
   </si>
@@ -171,6 +171,15 @@
   </si>
   <si>
     <t>"-99.7791", "contact_author"</t>
+  </si>
+  <si>
+    <t>slope_aspect</t>
+  </si>
+  <si>
+    <t>Whether the aspect of the slope transects was NES (0° - 180°) or NWS (181° - 359°). N/A was entered for non-slope transects.</t>
+  </si>
+  <si>
+    <t>"NWS", "NES", "N/A"</t>
   </si>
 </sst>
 </file>
@@ -506,7 +515,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B7125E7-DFAE-4BF5-9464-A5069826A029}">
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:C26"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="32.05078125" customWidth="1"/>
@@ -549,173 +558,184 @@
     </row>
     <row r="4" spans="1:3" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B5" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C5" t="s">
         <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="72" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C5" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C6" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="72" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B7" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C7" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" t="s">
+    <row r="8" spans="1:3" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B8" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C8" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" t="s">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B9" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C9" t="s">
         <v>20</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="72" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" t="s">
-        <v>21</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C9" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C10" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C11" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" t="s">
+        <v>23</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C12" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="72" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" t="s">
         <v>24</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B13" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C13" t="s">
         <v>43</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" t="s">
-        <v>25</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C13" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C14" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C15" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" t="s">
+        <v>31</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C16" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" t="s">
         <v>3</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B17" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C17" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B17" s="2"/>
-    </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="B18" s="2"/>
     </row>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="B19" s="2"/>
     </row>
-    <row r="20" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="B20" s="2"/>
     </row>
-    <row r="21" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="B21" s="2"/>
     </row>
-    <row r="22" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="B22" s="2"/>
     </row>
-    <row r="23" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="B23" s="2"/>
     </row>
-    <row r="24" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="B24" s="2"/>
     </row>
-    <row r="25" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="B25" s="2"/>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B26" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
